--- a/previews/stock.xlsx
+++ b/previews/stock.xlsx
@@ -104,6 +104,121 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4E79A7"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>Alat tulis</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Kertas</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Elektronik</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>4237000</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>12340000</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>7797000</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="60"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:tickLblPos val="low"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5842000" cy="1270000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="5842000" cy="1270000"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
@@ -351,7 +466,7 @@
         <v>3072000</v>
       </c>
     </row>
-    <row>
+    <row ht="100.0" customHeight="1">
       <c s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Nilai persediaan per kategori</t>
@@ -368,5 +483,6 @@
       </c>
     </row>
   </sheetData>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>